--- a/files/2026-09-04/RTL_vs_competitors_price_diff_2026-09-04.xlsx
+++ b/files/2026-09-04/RTL_vs_competitors_price_diff_2026-09-04.xlsx
@@ -169,6 +169,753 @@
     <t xml:space="preserve">Froza</t>
   </si>
   <si>
+    <t xml:space="preserve">08886-02805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Япония), (4л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5318.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5888.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4749.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-569.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4928.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-390.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5795.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">477.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">257 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5730.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">412.2600000000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 569 руб. (10.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 4 749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08886-81875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota CVTF Fluid FE, для вариаторов, (Таиланд), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4830.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5507.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4561.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-269.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1686 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4510.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-320.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6090.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1260.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">254 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5153.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.65999999999985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 320 руб. (6.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 4 510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08886-81885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Таиланд), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4414.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5032.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4337.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-77.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4076.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-337.80999999999995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5325.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4782.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">368.0799999999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 338 руб. (7.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 4 076.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-337.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Febi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6248.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5763.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-485.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5940.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-308.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6163.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 5 763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4024610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Япония), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3621.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4128.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3329.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-292.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3476.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-145.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3940.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4051.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">430.71000000000004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 292 руб. (8.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550061548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercedes-Benz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3496.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3527.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2973.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-523.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 523 руб. (15.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83215A1C740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло BMW Twin Power Turbo SN 0W-30 Longlife-12 FE (C2), (Германия/Испания), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2041.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2260.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1914.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-127.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 127 руб. (6.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 1 914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989320911ABDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1684.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1920.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1065.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-619.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1163.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-520.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 619 руб. (36.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-36.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989440411FULW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1790.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1436.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-354.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-294.5899999999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2035.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">245.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 354 руб. (19.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989671011FBDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1240.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1414.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1171.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-69.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1186 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1112.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-127.90000000000009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 128 руб. (10.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 1 112.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-127.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989681011FSEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">975.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1112.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-64.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7713 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">938.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-36.700000000000045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1165.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 64 руб. (6.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989681013FSEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5088.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5801.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-527.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-578.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 578 руб. (11.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691011FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1258.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1435.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1028.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-230.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1402 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1056.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-202.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 230 руб. (18.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-18.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691013FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5480.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4836.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-644.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1786 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5016.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-464.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 644 руб. (11.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 4 836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM10038-4EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3332.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3799.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2775.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-557.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2860.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-472.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 557 руб. (16.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2806.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3199.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2337.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-469.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2842.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.51000000000022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 469 руб. (16.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3912.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4331.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3197.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-715.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">256 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3323.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-589.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 715 руб. (18.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XT5QMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">791.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">902.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">728.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-63.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2709 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">751.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-39.700000000000045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">890.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.20000000000005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 63 руб. (8.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">08880-83717</t>
   </si>
   <si>
@@ -208,7 +955,7 @@
     <t xml:space="preserve">520.71</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 32 руб. (1.2%)</t>
+    <t xml:space="preserve">конкурент ниже на 32 руб. (1.2%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 2 561</t>
@@ -217,324 +964,6 @@
     <t xml:space="preserve">-1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">08886-02805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Япония), (4л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5318.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5888.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4749.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-569.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4928.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-390.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5795.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">477.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5730.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">412.2600000000002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 569 руб. (10.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 4 749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08886-81875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota CVTF Fluid FE, для вариаторов, (Таиланд), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4830.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5507.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4561.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-269.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1686 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4510.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-320.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6090.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1260.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">254 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5153.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.65999999999985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 320 руб. (6.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 4 510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08886-81885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Toyota ATF WS, для АКПП, (Таиланд), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4414.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5032.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4337.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-77.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4076.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-337.80999999999995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5325.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">911.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4782.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">368.0799999999999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 338 руб. (7.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 4 076.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-337.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Febi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6248.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5763.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-485.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5940.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-308.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6163.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 5 763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4024610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Япония), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitsubishi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3621.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4128.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3329.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-292.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3476.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-145.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3940.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4051.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">430.71000000000004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 292 руб. (8.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">550061548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercedes-Benz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3496.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3527.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2973.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-523.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 523 руб. (15.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-15.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83215A1C740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло BMW Twin Power Turbo SN 0W-30 Longlife-12 FE (C2), (Германия/Испания), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2041.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2260.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1914.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-127.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 127 руб. (6.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 1 914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">83215B5BFA4</t>
   </si>
   <si>
@@ -562,7 +991,7 @@
     <t xml:space="preserve">146.96000000000004</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 31 руб. (2.2%)</t>
+    <t xml:space="preserve">конкурент ниже на 31 руб. (2.2%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 386</t>
@@ -571,42 +1000,6 @@
     <t xml:space="preserve">-2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989320911ABDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1684.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1920.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1065.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-619.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1163.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-520.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 619 руб. (36.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-36.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">A000989440411FDNE</t>
   </si>
   <si>
@@ -628,7 +1021,7 @@
     <t xml:space="preserve">-59.1099999999999</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 59 руб. (3.5%)</t>
+    <t xml:space="preserve">конкурент ниже на 59 руб. (3.5%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 627.89</t>
@@ -640,237 +1033,6 @@
     <t xml:space="preserve">-3.5</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989440411FULW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1790.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1436.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-354.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">911 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-294.5899999999999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2035.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">245.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 354 руб. (19.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-19.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989671011FBDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1240.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1414.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1171.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-69.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1186 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1112.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-127.90000000000009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 128 руб. (10.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 1 112.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-127.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989681011FSEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">975.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1112.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-64.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7713 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">938.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-36.700000000000045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1165.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 64 руб. (6.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989681013FSEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5088.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5801.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-527.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-578.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 578 руб. (11.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691011FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1258.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1435.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1028.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-230.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1402 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1056.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-202.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 230 руб. (18.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-18.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691013FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5480.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4836.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-644.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1786 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5016.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-464.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 644 руб. (11.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 4 836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">KE90799932</t>
   </si>
   <si>
@@ -907,175 +1069,13 @@
     <t xml:space="preserve">537.9000000000001</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 14 руб. (0.8%)</t>
+    <t xml:space="preserve">конкурент ниже на 14 руб. (0.8%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 1 782</t>
   </si>
   <si>
     <t xml:space="preserve">-0.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM10038-4EN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3332.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3799.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2775.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-557.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2860.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-472.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 557 руб. (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2806.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3199.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2337.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-469.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2842.51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.51000000000022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 469 руб. (16.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3912.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4331.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3197.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-715.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">256 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3323.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-589.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 715 руб. (18.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XT5QMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">791.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">902.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">728.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-63.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2709 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">751.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-39.700000000000045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">890.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.20000000000005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 63 руб. (8.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.0</t>
   </si>
   <si>
     <t xml:space="preserve">08234P99F4PY1</t>
@@ -1684,7 +1684,7 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -1693,49 +1693,49 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>57</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" t="s">
         <v>58</v>
       </c>
-      <c r="I3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>59</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
         <v>60</v>
       </c>
-      <c r="L3" t="s">
+      <c r="N3" t="s">
         <v>61</v>
-      </c>
-      <c r="M3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N3" t="s">
-        <v>63</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="S3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1750,16 +1750,16 @@
         <v>39</v>
       </c>
       <c r="Y3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AC3" t="s">
         <v>52</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
@@ -1782,49 +1782,49 @@
         <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" t="s">
         <v>73</v>
       </c>
-      <c r="I4" t="s">
-        <v>72</v>
-      </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L4" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="M4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O4" t="s">
         <v>42</v>
       </c>
       <c r="P4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="S4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1839,16 +1839,16 @@
         <v>39</v>
       </c>
       <c r="Y4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AA4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AB4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC4" t="s">
         <v>52</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
@@ -1871,49 +1871,49 @@
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O5" t="s">
         <v>42</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R5" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="S5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U5" t="s">
         <v>42</v>
@@ -1928,16 +1928,16 @@
         <v>39</v>
       </c>
       <c r="Y5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AA5" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="AB5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AC5" t="s">
         <v>52</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1960,49 +1960,49 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I6" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="J6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L6" t="s">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="M6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="Q6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R6" t="s">
+        <v>39</v>
+      </c>
+      <c r="S6" t="s">
         <v>115</v>
       </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>116</v>
-      </c>
-      <c r="T6" t="s">
-        <v>117</v>
       </c>
       <c r="U6" t="s">
         <v>42</v>
@@ -2017,16 +2017,16 @@
         <v>39</v>
       </c>
       <c r="Y6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z6" t="s">
         <v>118</v>
       </c>
-      <c r="Z6" t="s">
-        <v>119</v>
-      </c>
       <c r="AA6" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="AB6" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="AC6" t="s">
         <v>52</v>
@@ -2034,13 +2034,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -2049,49 +2049,49 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" t="s">
         <v>125</v>
       </c>
-      <c r="G7" t="s">
+      <c r="K7" t="s">
         <v>126</v>
       </c>
-      <c r="H7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>127</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>128</v>
       </c>
-      <c r="L7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>129</v>
-      </c>
-      <c r="N7" t="s">
-        <v>130</v>
       </c>
       <c r="O7" t="s">
         <v>42</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="Q7" t="s">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="R7" t="s">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="S7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="T7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="U7" t="s">
         <v>42</v>
@@ -2106,16 +2106,16 @@
         <v>39</v>
       </c>
       <c r="Y7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Z7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AA7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB7" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="AC7" t="s">
         <v>52</v>
@@ -2123,13 +2123,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -2138,87 +2138,87 @@
         <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L8" t="s">
-        <v>143</v>
+        <v>39</v>
       </c>
       <c r="M8" t="s">
-        <v>144</v>
+        <v>39</v>
       </c>
       <c r="N8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" t="s">
+        <v>39</v>
+      </c>
+      <c r="P8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" t="s">
+        <v>39</v>
+      </c>
+      <c r="S8" t="s">
+        <v>39</v>
+      </c>
+      <c r="T8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W8" t="s">
+        <v>39</v>
+      </c>
+      <c r="X8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA8" t="s">
         <v>145</v>
       </c>
-      <c r="O8" t="s">
-        <v>42</v>
-      </c>
-      <c r="P8" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>147</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="AB8" t="s">
         <v>148</v>
       </c>
-      <c r="S8" t="s">
-        <v>149</v>
-      </c>
-      <c r="T8" t="s">
-        <v>150</v>
-      </c>
-      <c r="U8" t="s">
-        <v>42</v>
-      </c>
-      <c r="V8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W8" t="s">
-        <v>39</v>
-      </c>
-      <c r="X8" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>151</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>142</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>153</v>
-      </c>
       <c r="AC8" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2227,73 +2227,73 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" t="s">
+        <v>154</v>
+      </c>
+      <c r="N9" t="s">
+        <v>155</v>
+      </c>
+      <c r="O9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" t="s">
+        <v>39</v>
+      </c>
+      <c r="T9" t="s">
+        <v>39</v>
+      </c>
+      <c r="U9" t="s">
+        <v>39</v>
+      </c>
+      <c r="V9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" t="s">
+        <v>39</v>
+      </c>
+      <c r="X9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z9" t="s">
         <v>157</v>
       </c>
-      <c r="G9" t="s">
+      <c r="AA9" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB9" t="s">
         <v>158</v>
-      </c>
-      <c r="H9" t="s">
-        <v>159</v>
-      </c>
-      <c r="I9" t="s">
-        <v>158</v>
-      </c>
-      <c r="J9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K9" t="s">
-        <v>161</v>
-      </c>
-      <c r="L9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>39</v>
-      </c>
-      <c r="R9" t="s">
-        <v>39</v>
-      </c>
-      <c r="S9" t="s">
-        <v>39</v>
-      </c>
-      <c r="T9" t="s">
-        <v>39</v>
-      </c>
-      <c r="U9" t="s">
-        <v>39</v>
-      </c>
-      <c r="V9" t="s">
-        <v>39</v>
-      </c>
-      <c r="W9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X9" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>164</v>
       </c>
       <c r="AC9" t="s">
         <v>39</v>
@@ -2301,13 +2301,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -2316,31 +2316,31 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H10" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I10" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="L10" t="s">
         <v>39</v>
       </c>
       <c r="M10" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="O10" t="s">
         <v>42</v>
@@ -2373,16 +2373,16 @@
         <v>39</v>
       </c>
       <c r="Y10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="Z10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="AA10" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AB10" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AC10" t="s">
         <v>39</v>
@@ -2390,13 +2390,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2405,87 +2405,87 @@
         <v>33</v>
       </c>
       <c r="F11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" t="s">
+        <v>174</v>
+      </c>
+      <c r="J11" t="s">
+        <v>175</v>
+      </c>
+      <c r="K11" t="s">
+        <v>176</v>
+      </c>
+      <c r="L11" t="s">
         <v>177</v>
       </c>
-      <c r="G11" t="s">
+      <c r="M11" t="s">
         <v>178</v>
       </c>
-      <c r="H11" t="s">
+      <c r="N11" t="s">
         <v>179</v>
-      </c>
-      <c r="I11" t="s">
-        <v>178</v>
-      </c>
-      <c r="J11" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" t="s">
-        <v>180</v>
-      </c>
-      <c r="N11" t="s">
-        <v>181</v>
       </c>
       <c r="O11" t="s">
         <v>42</v>
       </c>
       <c r="P11" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="Q11" t="s">
-        <v>39</v>
+        <v>181</v>
       </c>
       <c r="R11" t="s">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="S11" t="s">
-        <v>182</v>
+        <v>39</v>
       </c>
       <c r="T11" t="s">
+        <v>39</v>
+      </c>
+      <c r="U11" t="s">
+        <v>39</v>
+      </c>
+      <c r="V11" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y11" t="s">
         <v>183</v>
       </c>
-      <c r="U11" t="s">
-        <v>42</v>
-      </c>
-      <c r="V11" t="s">
-        <v>39</v>
-      </c>
-      <c r="W11" t="s">
-        <v>39</v>
-      </c>
-      <c r="X11" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y11" t="s">
+      <c r="Z11" t="s">
         <v>184</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AA11" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB11" t="s">
         <v>185</v>
       </c>
-      <c r="AA11" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>186</v>
-      </c>
       <c r="AC11" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" t="s">
         <v>187</v>
       </c>
-      <c r="B12" t="s">
-        <v>188</v>
-      </c>
       <c r="C12" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -2494,25 +2494,25 @@
         <v>33</v>
       </c>
       <c r="F12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G12" t="s">
         <v>189</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>190</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
+        <v>189</v>
+      </c>
+      <c r="J12" t="s">
         <v>191</v>
       </c>
-      <c r="I12" t="s">
-        <v>190</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>192</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>193</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
       </c>
       <c r="M12" t="s">
         <v>194</v>
@@ -2557,10 +2557,10 @@
         <v>197</v>
       </c>
       <c r="AA12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AB12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC12" t="s">
         <v>39</v>
@@ -2568,13 +2568,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -2583,43 +2583,43 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H13" t="s">
+        <v>204</v>
+      </c>
+      <c r="I13" t="s">
         <v>203</v>
       </c>
-      <c r="I13" t="s">
-        <v>202</v>
-      </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="L13" t="s">
-        <v>39</v>
+        <v>206</v>
       </c>
       <c r="M13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="O13" t="s">
         <v>42</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>209</v>
       </c>
       <c r="Q13" t="s">
-        <v>39</v>
+        <v>210</v>
       </c>
       <c r="R13" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="S13" t="s">
         <v>39</v>
@@ -2640,16 +2640,16 @@
         <v>39</v>
       </c>
       <c r="Y13" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Z13" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AA13" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AB13" t="s">
-        <v>209</v>
+        <v>87</v>
       </c>
       <c r="AC13" t="s">
         <v>39</v>
@@ -2657,13 +2657,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C14" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -2672,73 +2672,73 @@
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H14" t="s">
-        <v>168</v>
+        <v>217</v>
       </c>
       <c r="I14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J14" t="s">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L14" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M14" t="s">
-        <v>217</v>
+        <v>78</v>
       </c>
       <c r="N14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O14" t="s">
         <v>42</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>39</v>
       </c>
       <c r="Q14" t="s">
+        <v>39</v>
+      </c>
+      <c r="R14" t="s">
+        <v>39</v>
+      </c>
+      <c r="S14" t="s">
+        <v>39</v>
+      </c>
+      <c r="T14" t="s">
+        <v>39</v>
+      </c>
+      <c r="U14" t="s">
+        <v>39</v>
+      </c>
+      <c r="V14" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" t="s">
+        <v>39</v>
+      </c>
+      <c r="X14" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA14" t="s">
         <v>220</v>
       </c>
-      <c r="R14" t="s">
-        <v>221</v>
-      </c>
-      <c r="S14" t="s">
-        <v>39</v>
-      </c>
-      <c r="T14" t="s">
-        <v>39</v>
-      </c>
-      <c r="U14" t="s">
-        <v>39</v>
-      </c>
-      <c r="V14" t="s">
-        <v>39</v>
-      </c>
-      <c r="W14" t="s">
-        <v>39</v>
-      </c>
-      <c r="X14" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y14" t="s">
+      <c r="AB14" t="s">
         <v>222</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>224</v>
       </c>
       <c r="AC14" t="s">
         <v>39</v>
@@ -2746,13 +2746,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -2761,31 +2761,31 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
+        <v>225</v>
+      </c>
+      <c r="G15" t="s">
+        <v>226</v>
+      </c>
+      <c r="H15" t="s">
         <v>227</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
+        <v>226</v>
+      </c>
+      <c r="J15" t="s">
         <v>228</v>
       </c>
-      <c r="H15" t="s">
+      <c r="K15" t="s">
         <v>229</v>
       </c>
-      <c r="I15" t="s">
-        <v>228</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="L15" t="s">
         <v>230</v>
       </c>
-      <c r="K15" t="s">
+      <c r="M15" t="s">
         <v>231</v>
       </c>
-      <c r="L15" t="s">
+      <c r="N15" t="s">
         <v>232</v>
-      </c>
-      <c r="M15" t="s">
-        <v>233</v>
-      </c>
-      <c r="N15" t="s">
-        <v>234</v>
       </c>
       <c r="O15" t="s">
         <v>42</v>
@@ -2818,16 +2818,16 @@
         <v>39</v>
       </c>
       <c r="Y15" t="s">
+        <v>233</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>234</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB15" t="s">
         <v>235</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>237</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>238</v>
       </c>
       <c r="AC15" t="s">
         <v>39</v>
@@ -2835,13 +2835,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C16" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -2850,43 +2850,43 @@
         <v>33</v>
       </c>
       <c r="F16" t="s">
+        <v>238</v>
+      </c>
+      <c r="G16" t="s">
+        <v>239</v>
+      </c>
+      <c r="H16" t="s">
+        <v>110</v>
+      </c>
+      <c r="I16" t="s">
+        <v>239</v>
+      </c>
+      <c r="J16" t="s">
+        <v>240</v>
+      </c>
+      <c r="K16" t="s">
         <v>241</v>
       </c>
-      <c r="G16" t="s">
+      <c r="L16" t="s">
         <v>242</v>
       </c>
-      <c r="H16" t="s">
+      <c r="M16" t="s">
         <v>243</v>
       </c>
-      <c r="I16" t="s">
-        <v>242</v>
-      </c>
-      <c r="J16" t="s">
-        <v>115</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="N16" t="s">
         <v>244</v>
-      </c>
-      <c r="L16" t="s">
-        <v>245</v>
-      </c>
-      <c r="M16" t="s">
-        <v>246</v>
-      </c>
-      <c r="N16" t="s">
-        <v>247</v>
       </c>
       <c r="O16" t="s">
         <v>42</v>
       </c>
       <c r="P16" t="s">
-        <v>248</v>
+        <v>39</v>
       </c>
       <c r="Q16" t="s">
-        <v>249</v>
+        <v>39</v>
       </c>
       <c r="R16" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="S16" t="s">
         <v>39</v>
@@ -2907,16 +2907,16 @@
         <v>39</v>
       </c>
       <c r="Y16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Z16" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AA16" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AB16" t="s">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="AC16" t="s">
         <v>39</v>
@@ -2924,13 +2924,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B17" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -2939,31 +2939,31 @@
         <v>33</v>
       </c>
       <c r="F17" t="s">
+        <v>251</v>
+      </c>
+      <c r="G17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" t="s">
+        <v>253</v>
+      </c>
+      <c r="I17" t="s">
+        <v>252</v>
+      </c>
+      <c r="J17" t="s">
         <v>254</v>
       </c>
-      <c r="G17" t="s">
+      <c r="K17" t="s">
         <v>255</v>
       </c>
-      <c r="H17" t="s">
+      <c r="L17" t="s">
         <v>256</v>
       </c>
-      <c r="I17" t="s">
-        <v>255</v>
-      </c>
-      <c r="J17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
         <v>257</v>
       </c>
-      <c r="L17" t="s">
+      <c r="N17" t="s">
         <v>258</v>
-      </c>
-      <c r="M17" t="s">
-        <v>94</v>
-      </c>
-      <c r="N17" t="s">
-        <v>259</v>
       </c>
       <c r="O17" t="s">
         <v>42</v>
@@ -2996,13 +2996,13 @@
         <v>39</v>
       </c>
       <c r="Y17" t="s">
+        <v>259</v>
+      </c>
+      <c r="Z17" t="s">
         <v>260</v>
       </c>
-      <c r="Z17" t="s">
-        <v>102</v>
-      </c>
       <c r="AA17" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AB17" t="s">
         <v>261</v>
@@ -3019,7 +3019,7 @@
         <v>263</v>
       </c>
       <c r="C18" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -3049,31 +3049,31 @@
         <v>269</v>
       </c>
       <c r="M18" t="s">
+        <v>39</v>
+      </c>
+      <c r="N18" t="s">
+        <v>39</v>
+      </c>
+      <c r="O18" t="s">
+        <v>39</v>
+      </c>
+      <c r="P18" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>39</v>
+      </c>
+      <c r="R18" t="s">
+        <v>39</v>
+      </c>
+      <c r="S18" t="s">
         <v>270</v>
       </c>
-      <c r="N18" t="s">
+      <c r="T18" t="s">
         <v>271</v>
       </c>
-      <c r="O18" t="s">
+      <c r="U18" t="s">
         <v>42</v>
-      </c>
-      <c r="P18" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>39</v>
-      </c>
-      <c r="R18" t="s">
-        <v>39</v>
-      </c>
-      <c r="S18" t="s">
-        <v>39</v>
-      </c>
-      <c r="T18" t="s">
-        <v>39</v>
-      </c>
-      <c r="U18" t="s">
-        <v>39</v>
       </c>
       <c r="V18" t="s">
         <v>39</v>
@@ -3094,21 +3094,21 @@
         <v>268</v>
       </c>
       <c r="AB18" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="AC18" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>274</v>
+      </c>
+      <c r="B19" t="s">
         <v>275</v>
       </c>
-      <c r="B19" t="s">
-        <v>276</v>
-      </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -3117,16 +3117,16 @@
         <v>33</v>
       </c>
       <c r="F19" t="s">
+        <v>276</v>
+      </c>
+      <c r="G19" t="s">
         <v>277</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>278</v>
       </c>
-      <c r="H19" t="s">
-        <v>126</v>
-      </c>
       <c r="I19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J19" t="s">
         <v>279</v>
@@ -3183,7 +3183,7 @@
         <v>280</v>
       </c>
       <c r="AB19" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="AC19" t="s">
         <v>39</v>
@@ -3191,13 +3191,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>286</v>
+      </c>
+      <c r="B20" t="s">
         <v>287</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>288</v>
-      </c>
-      <c r="C20" t="s">
-        <v>289</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -3206,25 +3206,25 @@
         <v>33</v>
       </c>
       <c r="F20" t="s">
+        <v>289</v>
+      </c>
+      <c r="G20" t="s">
         <v>290</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>291</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
+        <v>290</v>
+      </c>
+      <c r="J20" t="s">
         <v>292</v>
       </c>
-      <c r="I20" t="s">
-        <v>291</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>293</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>294</v>
-      </c>
-      <c r="L20" t="s">
-        <v>39</v>
       </c>
       <c r="M20" t="s">
         <v>295</v>
@@ -3269,7 +3269,7 @@
         <v>300</v>
       </c>
       <c r="AA20" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AB20" t="s">
         <v>301</v>
@@ -3334,13 +3334,13 @@
         <v>39</v>
       </c>
       <c r="S21" t="s">
-        <v>39</v>
+        <v>313</v>
       </c>
       <c r="T21" t="s">
-        <v>39</v>
+        <v>314</v>
       </c>
       <c r="U21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V21" t="s">
         <v>39</v>
@@ -3352,30 +3352,30 @@
         <v>39</v>
       </c>
       <c r="Y21" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Z21" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA21" t="s">
         <v>309</v>
       </c>
       <c r="AB21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AC21" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B22" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C22" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D22" t="s">
         <v>32</v>
@@ -3384,34 +3384,34 @@
         <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G22" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H22" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I22" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J22" t="s">
-        <v>321</v>
+        <v>39</v>
       </c>
       <c r="K22" t="s">
-        <v>322</v>
+        <v>39</v>
       </c>
       <c r="L22" t="s">
+        <v>39</v>
+      </c>
+      <c r="M22" t="s">
         <v>323</v>
       </c>
-      <c r="M22" t="s">
-        <v>39</v>
-      </c>
       <c r="N22" t="s">
-        <v>39</v>
+        <v>324</v>
       </c>
       <c r="O22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P22" t="s">
         <v>39</v>
@@ -3423,10 +3423,10 @@
         <v>39</v>
       </c>
       <c r="S22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="T22" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="U22" t="s">
         <v>42</v>
@@ -3441,16 +3441,16 @@
         <v>39</v>
       </c>
       <c r="Y22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA22" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AB22" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="AC22" t="s">
         <v>52</v>
@@ -3458,13 +3458,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
         <v>32</v>
@@ -3473,31 +3473,31 @@
         <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J23" t="s">
-        <v>333</v>
+        <v>39</v>
       </c>
       <c r="K23" t="s">
-        <v>334</v>
+        <v>39</v>
       </c>
       <c r="L23" t="s">
+        <v>39</v>
+      </c>
+      <c r="M23" t="s">
         <v>335</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>336</v>
-      </c>
-      <c r="N23" t="s">
-        <v>337</v>
       </c>
       <c r="O23" t="s">
         <v>42</v>
@@ -3530,16 +3530,16 @@
         <v>39</v>
       </c>
       <c r="Y23" t="s">
+        <v>337</v>
+      </c>
+      <c r="Z23" t="s">
         <v>338</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AA23" t="s">
         <v>339</v>
       </c>
-      <c r="AA23" t="s">
-        <v>334</v>
-      </c>
       <c r="AB23" t="s">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="AC23" t="s">
         <v>39</v>
@@ -3547,13 +3547,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B24" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C24" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D24" t="s">
         <v>32</v>
@@ -3562,25 +3562,25 @@
         <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G24" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H24" t="s">
+        <v>346</v>
+      </c>
+      <c r="I24" t="s">
         <v>345</v>
       </c>
-      <c r="I24" t="s">
-        <v>344</v>
-      </c>
       <c r="J24" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L24" t="s">
-        <v>348</v>
+        <v>39</v>
       </c>
       <c r="M24" t="s">
         <v>349</v>
@@ -3625,7 +3625,7 @@
         <v>354</v>
       </c>
       <c r="AA24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AB24" t="s">
         <v>355</v>
@@ -3820,7 +3820,7 @@
         <v>387</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>304</v>
       </c>
       <c r="D27" t="s">
         <v>32</v>
@@ -3832,13 +3832,13 @@
         <v>388</v>
       </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>306</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="I27" t="s">
-        <v>57</v>
+        <v>306</v>
       </c>
       <c r="J27" t="s">
         <v>389</v>
@@ -3909,7 +3909,7 @@
         <v>397</v>
       </c>
       <c r="C28" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -3998,7 +3998,7 @@
         <v>410</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -4087,7 +4087,7 @@
         <v>428</v>
       </c>
       <c r="C30" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -4354,7 +4354,7 @@
         <v>459</v>
       </c>
       <c r="C33" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
         <v>32</v>
@@ -4366,13 +4366,13 @@
         <v>460</v>
       </c>
       <c r="G33" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="H33" t="s">
         <v>461</v>
       </c>
       <c r="I33" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -4443,7 +4443,7 @@
         <v>463</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -4532,7 +4532,7 @@
         <v>468</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
